--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_GAL.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_GAL.xlsx
@@ -1271,13 +1271,13 @@
         <v>79.5</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -1290,13 +1290,13 @@
         <v>93.5</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="4">
@@ -1309,13 +1309,13 @@
         <v>92.3</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.5</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="5">
@@ -1328,13 +1328,13 @@
         <v>1.2</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1347,7 +1347,7 @@
         <v>17.7</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -1404,13 +1404,13 @@
         <v>21.3</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
